--- a/data/trans_orig/P6903-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6903-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29727</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23502</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44372</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49604</t>
+          <t>49462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66085</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25543</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67200</t>
+          <t>67896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88070</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37948</t>
+          <t>37489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59924</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47806</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73483</t>
+          <t>75416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86057</t>
+          <t>86453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108033</t>
+          <t>108492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33486</t>
+          <t>33975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46117</t>
+          <t>46134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125294</t>
+          <t>123361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>150971</t>
+          <t>150669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39103</t>
+          <t>39090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>31184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55622</t>
+          <t>55754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70841</t>
+          <t>70854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91325</t>
+          <t>91668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36859</t>
+          <t>36923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100855</t>
+          <t>100723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125753</t>
+          <t>125293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41365</t>
+          <t>41816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>63841</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67795</t>
+          <t>67212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96628</t>
+          <t>96541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>73208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95684</t>
+          <t>95233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>50082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67958</t>
+          <t>68319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128972</t>
+          <t>129059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157805</t>
+          <t>158388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128890</t>
+          <t>129613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170546</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55237</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83314</t>
+          <t>81376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192224</t>
+          <t>192104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242444</t>
+          <t>242897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301759</t>
+          <t>301622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343415</t>
+          <t>342692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>138745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>164884</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>449983</t>
+          <t>449530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>500203</t>
+          <t>500323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>26852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47961</t>
+          <t>48686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63686</t>
+          <t>63046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27491</t>
+          <t>27299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68507</t>
+          <t>68212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88183</t>
+          <t>87949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31561</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32306</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55117</t>
+          <t>55248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60245</t>
+          <t>61209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>77816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31251</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47814</t>
+          <t>47299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99038</t>
+          <t>98907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121849</t>
+          <t>121390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27437</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48244</t>
+          <t>49019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>48463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64870</t>
+          <t>64764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30646</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44160</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84292</t>
+          <t>83517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105099</t>
+          <t>104856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50342</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54192</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68636</t>
+          <t>68221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46925</t>
+          <t>48022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91157</t>
+          <t>91014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112853</t>
+          <t>112745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62308</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61107</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89027</t>
+          <t>88549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132031</t>
+          <t>129351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>175264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231652</t>
+          <t>230438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>261995</t>
+          <t>261024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125651</t>
+          <t>126129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153571</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364599</t>
+          <t>363717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406950</t>
+          <t>409630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26701</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>21990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39448</t>
+          <t>39176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27972</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>45412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>62598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>22206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44322</t>
+          <t>42932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32558</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>45782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70447</t>
+          <t>71590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52662</t>
+          <t>54052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73552</t>
+          <t>74778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>37570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82088</t>
+          <t>80945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107051</t>
+          <t>106753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>35162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55528</t>
+          <t>56441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61900</t>
+          <t>61206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87375</t>
+          <t>88431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54407</t>
+          <t>53494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75455</t>
+          <t>74773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27152</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42858</t>
+          <t>43527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87307</t>
+          <t>86251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112782</t>
+          <t>113476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48371</t>
+          <t>48433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51209</t>
+          <t>50694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75548</t>
+          <t>75305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40039</t>
+          <t>39977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58763</t>
+          <t>58397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49301</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78945</t>
+          <t>79188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103284</t>
+          <t>103799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117870</t>
+          <t>117715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154859</t>
+          <t>156230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>74264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105873</t>
+          <t>103788</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202214</t>
+          <t>202638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>250839</t>
+          <t>251475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195142</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232131</t>
+          <t>232286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110425</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139629</t>
+          <t>142034</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315460</t>
+          <t>314824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364085</t>
+          <t>363661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>28133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32340</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53608</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39030</t>
+          <t>39962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57712</t>
+          <t>58069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26802</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38969</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>71311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93557</t>
+          <t>93318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30815</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>54513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31780</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48423</t>
+          <t>48478</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67406</t>
+          <t>67699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97154</t>
+          <t>95754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>56357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80055</t>
+          <t>80407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50307</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66950</t>
+          <t>66450</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>113846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142194</t>
+          <t>141901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>45225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>23567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>67155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>39975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>51683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87184</t>
+          <t>85940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84546</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128387</t>
+          <t>127758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40803</t>
+          <t>40549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>40673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59286</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66730</t>
+          <t>66045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95452</t>
+          <t>95571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59549</t>
+          <t>59803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78678</t>
+          <t>79095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>62542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108115</t>
+          <t>107996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136837</t>
+          <t>137522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96638</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137275</t>
+          <t>133498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>101182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160985</t>
+          <t>160700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214441</t>
+          <t>209245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282906</t>
+          <t>282302</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199580</t>
+          <t>203357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>240217</t>
+          <t>240651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>192834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>253535</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407483</t>
+          <t>408087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>475948</t>
+          <t>481144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
